--- a/7 Future comparisons/Bonaire/output/yearly_population_growth_param_0.5.xlsx
+++ b/7 Future comparisons/Bonaire/output/yearly_population_growth_param_0.5.xlsx
@@ -790,10 +790,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11707</v>
+        <v>11975</v>
       </c>
       <c r="D2" t="n">
-        <v>96597</v>
+        <v>97255</v>
       </c>
     </row>
     <row r="3">
@@ -801,13 +801,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>271</v>
+        <v>508</v>
       </c>
       <c r="C3" t="n">
-        <v>3000</v>
+        <v>3673</v>
       </c>
       <c r="D3" t="n">
-        <v>61477</v>
+        <v>56485</v>
       </c>
     </row>
     <row r="4">
@@ -815,13 +815,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>814</v>
+        <v>1150</v>
       </c>
       <c r="C4" t="n">
-        <v>5501</v>
+        <v>5640</v>
       </c>
       <c r="D4" t="n">
-        <v>23171</v>
+        <v>21116</v>
       </c>
     </row>
     <row r="5">
@@ -829,13 +829,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>721</v>
+        <v>816</v>
       </c>
       <c r="C5" t="n">
-        <v>4073</v>
+        <v>3774</v>
       </c>
       <c r="D5" t="n">
-        <v>6754</v>
+        <v>6628</v>
       </c>
     </row>
     <row r="6">
@@ -843,13 +843,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>1215</v>
+        <v>1113</v>
       </c>
       <c r="D6" t="n">
-        <v>2932</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="7">
@@ -857,13 +857,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D7" t="n">
-        <v>1911</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="8">
@@ -871,13 +871,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>1558</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="9">
@@ -885,13 +885,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>1344</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="10">
@@ -899,13 +899,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D10" t="n">
-        <v>1108</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="11">
@@ -913,13 +913,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>935</v>
+        <v>975</v>
       </c>
     </row>
     <row r="12">
@@ -927,13 +927,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
-        <v>738</v>
+        <v>846</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>454</v>
+        <v>682</v>
       </c>
     </row>
     <row r="14">
@@ -955,13 +955,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>315</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15">
@@ -969,13 +969,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>186</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16">
@@ -983,13 +983,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17">
@@ -997,13 +997,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18">
@@ -1011,13 +1011,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -1101,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>16160</v>
+        <v>16641</v>
       </c>
       <c r="D2" t="n">
-        <v>85005</v>
+        <v>86559</v>
       </c>
     </row>
     <row r="3">
@@ -1112,13 +1112,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="C3" t="n">
-        <v>6475</v>
+        <v>6613</v>
       </c>
       <c r="D3" t="n">
-        <v>62347</v>
+        <v>57526</v>
       </c>
     </row>
     <row r="4">
@@ -1126,13 +1126,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>476</v>
+        <v>716</v>
       </c>
       <c r="C4" t="n">
-        <v>4142</v>
+        <v>4505</v>
       </c>
       <c r="D4" t="n">
-        <v>27837</v>
+        <v>25227</v>
       </c>
     </row>
     <row r="5">
@@ -1140,13 +1140,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>706</v>
+        <v>872</v>
       </c>
       <c r="C5" t="n">
-        <v>4765</v>
+        <v>4554</v>
       </c>
       <c r="D5" t="n">
-        <v>8504</v>
+        <v>8170</v>
       </c>
     </row>
     <row r="6">
@@ -1154,13 +1154,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>436</v>
+        <v>481</v>
       </c>
       <c r="C6" t="n">
-        <v>2504</v>
+        <v>2342</v>
       </c>
       <c r="D6" t="n">
-        <v>3291</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="7">
@@ -1168,13 +1168,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>646</v>
+        <v>626</v>
       </c>
       <c r="D7" t="n">
-        <v>1990</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="8">
@@ -1182,13 +1182,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D8" t="n">
-        <v>1593</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="9">
@@ -1196,13 +1196,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D9" t="n">
-        <v>1384</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="10">
@@ -1210,13 +1210,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="11">
@@ -1224,13 +1224,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>935</v>
+        <v>969</v>
       </c>
     </row>
     <row r="12">
@@ -1238,13 +1238,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" t="n">
-        <v>711</v>
+        <v>851</v>
       </c>
     </row>
     <row r="13">
@@ -1252,13 +1252,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>440</v>
+        <v>684</v>
       </c>
     </row>
     <row r="14">
@@ -1266,13 +1266,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>295</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15">
@@ -1280,13 +1280,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>164</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16">
@@ -1294,13 +1294,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17">
@@ -1308,13 +1308,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
@@ -1322,13 +1322,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19">
@@ -1336,13 +1336,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12451</v>
+        <v>13175</v>
       </c>
       <c r="D2" t="n">
-        <v>151212</v>
+        <v>154283</v>
       </c>
     </row>
     <row r="3">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="C3" t="n">
-        <v>9835</v>
+        <v>9691</v>
       </c>
       <c r="D3" t="n">
-        <v>61592</v>
+        <v>57047</v>
       </c>
     </row>
     <row r="4">
@@ -1437,13 +1437,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>257</v>
+        <v>411</v>
       </c>
       <c r="C4" t="n">
-        <v>5260</v>
+        <v>5339</v>
       </c>
       <c r="D4" t="n">
-        <v>31297</v>
+        <v>28248</v>
       </c>
     </row>
     <row r="5">
@@ -1451,13 +1451,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>559</v>
+        <v>721</v>
       </c>
       <c r="C5" t="n">
-        <v>4418</v>
+        <v>4349</v>
       </c>
       <c r="D5" t="n">
-        <v>10554</v>
+        <v>9971</v>
       </c>
     </row>
     <row r="6">
@@ -1465,13 +1465,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>532</v>
+        <v>615</v>
       </c>
       <c r="C6" t="n">
-        <v>3527</v>
+        <v>3294</v>
       </c>
       <c r="D6" t="n">
-        <v>3783</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="7">
@@ -1479,13 +1479,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="C7" t="n">
-        <v>1423</v>
+        <v>1393</v>
       </c>
       <c r="D7" t="n">
-        <v>2091</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="8">
@@ -1493,13 +1493,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="D8" t="n">
-        <v>1631</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="9">
@@ -1507,13 +1507,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D9" t="n">
-        <v>1411</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="10">
@@ -1524,10 +1524,10 @@
         <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D10" t="n">
-        <v>1124</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="11">
@@ -1535,13 +1535,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>926</v>
+        <v>964</v>
       </c>
     </row>
     <row r="12">
@@ -1549,13 +1549,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>688</v>
+        <v>846</v>
       </c>
     </row>
     <row r="13">
@@ -1563,13 +1563,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
         <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>427</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14">
@@ -1577,13 +1577,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>276</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15">
@@ -1591,13 +1591,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>143</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16">
@@ -1605,13 +1605,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17">
@@ -1619,13 +1619,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18">
@@ -1633,13 +1633,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
@@ -1647,13 +1647,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>15960</v>
+        <v>16392</v>
       </c>
       <c r="D2" t="n">
-        <v>142202</v>
+        <v>145735</v>
       </c>
     </row>
     <row r="3">
@@ -1734,13 +1734,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>9795</v>
+        <v>9859</v>
       </c>
       <c r="D3" t="n">
-        <v>67758</v>
+        <v>63004</v>
       </c>
     </row>
     <row r="4">
@@ -1748,13 +1748,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="C4" t="n">
-        <v>7353</v>
+        <v>7056</v>
       </c>
       <c r="D4" t="n">
-        <v>33835</v>
+        <v>30435</v>
       </c>
     </row>
     <row r="5">
@@ -1762,13 +1762,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>403</v>
+        <v>533</v>
       </c>
       <c r="C5" t="n">
-        <v>4740</v>
+        <v>4634</v>
       </c>
       <c r="D5" t="n">
-        <v>12524</v>
+        <v>11677</v>
       </c>
     </row>
     <row r="6">
@@ -1776,13 +1776,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>521</v>
+        <v>616</v>
       </c>
       <c r="C6" t="n">
-        <v>3932</v>
+        <v>3635</v>
       </c>
       <c r="D6" t="n">
-        <v>4359</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="7">
@@ -1790,13 +1790,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="C7" t="n">
-        <v>2240</v>
+        <v>2179</v>
       </c>
       <c r="D7" t="n">
-        <v>2206</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="8">
@@ -1804,13 +1804,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>722</v>
+        <v>774</v>
       </c>
       <c r="D8" t="n">
-        <v>1652</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="9">
@@ -1818,13 +1818,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>1452</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="10">
@@ -1832,13 +1832,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>1124</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="11">
@@ -1846,13 +1846,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>916</v>
+        <v>961</v>
       </c>
     </row>
     <row r="12">
@@ -1860,13 +1860,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>666</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13">
@@ -1874,13 +1874,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>413</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14">
@@ -1891,10 +1891,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>256</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15">
@@ -1902,13 +1902,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>124</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16">
@@ -1916,13 +1916,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17">
@@ -1930,13 +1930,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
@@ -1944,13 +1944,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1958,13 +1958,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -1975,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>17117</v>
+        <v>17387</v>
       </c>
       <c r="D2" t="n">
-        <v>201822</v>
+        <v>203989</v>
       </c>
     </row>
     <row r="3">
@@ -2045,13 +2045,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>11078</v>
+        <v>10997</v>
       </c>
       <c r="D3" t="n">
-        <v>70893</v>
+        <v>67821</v>
       </c>
     </row>
     <row r="4">
@@ -2059,13 +2059,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="C4" t="n">
-        <v>8349</v>
+        <v>7971</v>
       </c>
       <c r="D4" t="n">
-        <v>37039</v>
+        <v>32656</v>
       </c>
     </row>
     <row r="5">
@@ -2073,13 +2073,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>276</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>5765</v>
+        <v>5401</v>
       </c>
       <c r="D5" t="n">
-        <v>14309</v>
+        <v>13190</v>
       </c>
     </row>
     <row r="6">
@@ -2087,13 +2087,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>458</v>
+        <v>538</v>
       </c>
       <c r="C6" t="n">
-        <v>4247</v>
+        <v>3961</v>
       </c>
       <c r="D6" t="n">
-        <v>4934</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="7">
@@ -2101,13 +2101,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>2896</v>
+        <v>2727</v>
       </c>
       <c r="D7" t="n">
-        <v>2374</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="8">
@@ -2115,13 +2115,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>1219</v>
+        <v>1295</v>
       </c>
       <c r="D8" t="n">
-        <v>1673</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="9">
@@ -2129,13 +2129,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>414</v>
       </c>
       <c r="D9" t="n">
-        <v>1488</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="10">
@@ -2143,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>1113</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="11">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>911</v>
+        <v>956</v>
       </c>
     </row>
     <row r="12">
@@ -2171,13 +2171,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>642</v>
+        <v>843</v>
       </c>
     </row>
     <row r="13">
@@ -2185,13 +2185,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>393</v>
+        <v>696</v>
       </c>
     </row>
     <row r="14">
@@ -2199,13 +2199,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>236</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15">
@@ -2213,13 +2213,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>106</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16">
@@ -2227,13 +2227,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17">
@@ -2241,13 +2241,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
@@ -2255,13 +2255,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
@@ -2269,13 +2269,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2345,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>33088</v>
+        <v>32090</v>
       </c>
       <c r="D2" t="n">
-        <v>157065</v>
+        <v>158377</v>
       </c>
     </row>
     <row r="3">
@@ -2356,13 +2356,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>12056</v>
+        <v>11831</v>
       </c>
       <c r="D3" t="n">
-        <v>78331</v>
+        <v>75897</v>
       </c>
     </row>
     <row r="4">
@@ -2370,13 +2370,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>9275</v>
+        <v>8756</v>
       </c>
       <c r="D4" t="n">
-        <v>39843</v>
+        <v>35376</v>
       </c>
     </row>
     <row r="5">
@@ -2384,13 +2384,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="C5" t="n">
-        <v>6692</v>
+        <v>6174</v>
       </c>
       <c r="D5" t="n">
-        <v>15837</v>
+        <v>14531</v>
       </c>
     </row>
     <row r="6">
@@ -2398,13 +2398,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="C6" t="n">
-        <v>4794</v>
+        <v>4402</v>
       </c>
       <c r="D6" t="n">
-        <v>5644</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="7">
@@ -2412,13 +2412,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>3401</v>
+        <v>3107</v>
       </c>
       <c r="D7" t="n">
-        <v>2523</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="8">
@@ -2426,13 +2426,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="C8" t="n">
-        <v>1723</v>
+        <v>1787</v>
       </c>
       <c r="D8" t="n">
-        <v>1730</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="9">
@@ -2440,13 +2440,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>707</v>
       </c>
       <c r="D9" t="n">
-        <v>1492</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="10">
@@ -2454,13 +2454,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>1111</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="11">
@@ -2468,13 +2468,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>895</v>
+        <v>949</v>
       </c>
     </row>
     <row r="12">
@@ -2482,13 +2482,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>618</v>
+        <v>836</v>
       </c>
     </row>
     <row r="13">
@@ -2499,10 +2499,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>375</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14">
@@ -2510,13 +2510,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>214</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15">
@@ -2524,13 +2524,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16">
@@ -2538,13 +2538,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17">
@@ -2552,13 +2552,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
@@ -2566,13 +2566,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
@@ -2580,13 +2580,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -2597,10 +2597,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>23216</v>
+        <v>23596</v>
       </c>
       <c r="D2" t="n">
-        <v>198826</v>
+        <v>198784</v>
       </c>
     </row>
     <row r="3">
@@ -2667,13 +2667,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>17797</v>
+        <v>16367</v>
       </c>
       <c r="D3" t="n">
-        <v>81499</v>
+        <v>78245</v>
       </c>
     </row>
     <row r="4">
@@ -2681,13 +2681,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>10239</v>
+        <v>9438</v>
       </c>
       <c r="D4" t="n">
-        <v>42326</v>
+        <v>37850</v>
       </c>
     </row>
     <row r="5">
@@ -2695,13 +2695,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="C5" t="n">
-        <v>7534</v>
+        <v>6853</v>
       </c>
       <c r="D5" t="n">
-        <v>17581</v>
+        <v>16090</v>
       </c>
     </row>
     <row r="6">
@@ -2709,13 +2709,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="C6" t="n">
-        <v>5425</v>
+        <v>4862</v>
       </c>
       <c r="D6" t="n">
-        <v>6318</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="7">
@@ -2723,13 +2723,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>3856</v>
+        <v>3506</v>
       </c>
       <c r="D7" t="n">
-        <v>2674</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="8">
@@ -2737,13 +2737,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>310</v>
       </c>
       <c r="C8" t="n">
-        <v>2199</v>
+        <v>2178</v>
       </c>
       <c r="D8" t="n">
-        <v>1767</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="9">
@@ -2751,13 +2751,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="C9" t="n">
-        <v>869</v>
+        <v>1049</v>
       </c>
       <c r="D9" t="n">
-        <v>1508</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="10">
@@ -2765,13 +2765,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>366</v>
       </c>
       <c r="D10" t="n">
-        <v>1106</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="11">
@@ -2779,13 +2779,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>876</v>
+        <v>951</v>
       </c>
     </row>
     <row r="12">
@@ -2793,13 +2793,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>592</v>
+        <v>828</v>
       </c>
     </row>
     <row r="13">
@@ -2807,13 +2807,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>353</v>
+        <v>692</v>
       </c>
     </row>
     <row r="14">
@@ -2821,13 +2821,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>193</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15">
@@ -2835,13 +2835,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
@@ -2849,13 +2849,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -2863,13 +2863,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
@@ -2877,13 +2877,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
@@ -2891,13 +2891,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -2908,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2967,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>24537</v>
+        <v>24269</v>
       </c>
       <c r="D2" t="n">
-        <v>184335</v>
+        <v>184214</v>
       </c>
     </row>
     <row r="3">
@@ -2978,13 +2978,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>17635</v>
+        <v>16724</v>
       </c>
       <c r="D3" t="n">
-        <v>87103</v>
+        <v>82667</v>
       </c>
     </row>
     <row r="4">
@@ -2992,13 +2992,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>12808</v>
+        <v>11189</v>
       </c>
       <c r="D4" t="n">
-        <v>44423</v>
+        <v>39826</v>
       </c>
     </row>
     <row r="5">
@@ -3006,13 +3006,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="C5" t="n">
-        <v>8332</v>
+        <v>7438</v>
       </c>
       <c r="D5" t="n">
-        <v>19115</v>
+        <v>17326</v>
       </c>
     </row>
     <row r="6">
@@ -3020,13 +3020,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="C6" t="n">
-        <v>6016</v>
+        <v>5327</v>
       </c>
       <c r="D6" t="n">
-        <v>6956</v>
+        <v>7196</v>
       </c>
     </row>
     <row r="7">
@@ -3034,13 +3034,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>4375</v>
+        <v>3882</v>
       </c>
       <c r="D7" t="n">
-        <v>2815</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="8">
@@ -3048,13 +3048,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="C8" t="n">
-        <v>2625</v>
+        <v>2524</v>
       </c>
       <c r="D8" t="n">
-        <v>1813</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="9">
@@ -3062,13 +3062,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="C9" t="n">
-        <v>1163</v>
+        <v>1370</v>
       </c>
       <c r="D9" t="n">
-        <v>1502</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="10">
@@ -3076,13 +3076,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>370</v>
+        <v>552</v>
       </c>
       <c r="D10" t="n">
-        <v>1089</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="11">
@@ -3090,13 +3090,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>856</v>
+        <v>942</v>
       </c>
     </row>
     <row r="12">
@@ -3104,13 +3104,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>567</v>
+        <v>821</v>
       </c>
     </row>
     <row r="13">
@@ -3118,13 +3118,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>333</v>
+        <v>695</v>
       </c>
     </row>
     <row r="14">
@@ -3132,13 +3132,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>171</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15">
@@ -3146,13 +3146,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16">
@@ -3160,13 +3160,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
@@ -3174,13 +3174,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
@@ -3188,13 +3188,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
@@ -3205,10 +3205,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -3219,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3278,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>24750</v>
+        <v>24047</v>
       </c>
       <c r="D2" t="n">
-        <v>200906</v>
+        <v>198790</v>
       </c>
     </row>
     <row r="3">
@@ -3289,13 +3289,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>18043</v>
+        <v>17223</v>
       </c>
       <c r="D3" t="n">
-        <v>90201</v>
+        <v>84801</v>
       </c>
     </row>
     <row r="4">
@@ -3303,13 +3303,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>14117</v>
+        <v>12282</v>
       </c>
       <c r="D4" t="n">
-        <v>46350</v>
+        <v>41523</v>
       </c>
     </row>
     <row r="5">
@@ -3317,13 +3317,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C5" t="n">
-        <v>9613</v>
+        <v>8184</v>
       </c>
       <c r="D5" t="n">
-        <v>20418</v>
+        <v>18360</v>
       </c>
     </row>
     <row r="6">
@@ -3331,13 +3331,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="C6" t="n">
-        <v>6682</v>
+        <v>5829</v>
       </c>
       <c r="D6" t="n">
-        <v>7461</v>
+        <v>7818</v>
       </c>
     </row>
     <row r="7">
@@ -3345,13 +3345,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>4834</v>
+        <v>4200</v>
       </c>
       <c r="D7" t="n">
-        <v>2976</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="8">
@@ -3359,13 +3359,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="C8" t="n">
-        <v>3044</v>
+        <v>2870</v>
       </c>
       <c r="D8" t="n">
-        <v>1876</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="9">
@@ -3373,13 +3373,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>205</v>
       </c>
       <c r="C9" t="n">
-        <v>1460</v>
+        <v>1647</v>
       </c>
       <c r="D9" t="n">
-        <v>1481</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="10">
@@ -3387,13 +3387,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="C10" t="n">
-        <v>509</v>
+        <v>762</v>
       </c>
       <c r="D10" t="n">
-        <v>1080</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="11">
@@ -3401,13 +3401,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>277</v>
       </c>
       <c r="D11" t="n">
-        <v>832</v>
+        <v>932</v>
       </c>
     </row>
     <row r="12">
@@ -3415,13 +3415,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>540</v>
+        <v>812</v>
       </c>
     </row>
     <row r="13">
@@ -3429,13 +3429,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>309</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14">
@@ -3443,13 +3443,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>151</v>
+        <v>525</v>
       </c>
     </row>
     <row r="15">
@@ -3457,13 +3457,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16">
@@ -3471,13 +3471,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17">
@@ -3485,13 +3485,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
@@ -3502,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
@@ -3516,10 +3516,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -3530,10 +3530,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -3544,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3589,10 +3589,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>30188</v>
+        <v>28302</v>
       </c>
       <c r="D2" t="n">
-        <v>168744</v>
+        <v>165795</v>
       </c>
     </row>
     <row r="3">
@@ -3603,10 +3603,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>18287</v>
+        <v>17264</v>
       </c>
       <c r="D3" t="n">
-        <v>92523</v>
+        <v>88432</v>
       </c>
     </row>
     <row r="4">
@@ -3614,13 +3614,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>14991</v>
+        <v>13189</v>
       </c>
       <c r="D4" t="n">
-        <v>48753</v>
+        <v>42770</v>
       </c>
     </row>
     <row r="5">
@@ -3628,13 +3628,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C5" t="n">
-        <v>10666</v>
+        <v>8879</v>
       </c>
       <c r="D5" t="n">
-        <v>21290</v>
+        <v>19182</v>
       </c>
     </row>
     <row r="6">
@@ -3642,13 +3642,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C6" t="n">
-        <v>7468</v>
+        <v>6269</v>
       </c>
       <c r="D6" t="n">
-        <v>8072</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="7">
@@ -3656,13 +3656,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C7" t="n">
-        <v>5314</v>
+        <v>4572</v>
       </c>
       <c r="D7" t="n">
-        <v>3125</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="8">
@@ -3670,13 +3670,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="C8" t="n">
-        <v>3440</v>
+        <v>3138</v>
       </c>
       <c r="D8" t="n">
-        <v>1892</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="9">
@@ -3684,13 +3684,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="C9" t="n">
-        <v>1753</v>
+        <v>1929</v>
       </c>
       <c r="D9" t="n">
-        <v>1471</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="10">
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C10" t="n">
-        <v>658</v>
+        <v>954</v>
       </c>
       <c r="D10" t="n">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="11">
@@ -3712,13 +3712,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>385</v>
       </c>
       <c r="D11" t="n">
-        <v>808</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12">
@@ -3726,13 +3726,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>513</v>
+        <v>802</v>
       </c>
     </row>
     <row r="13">
@@ -3740,13 +3740,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>285</v>
+        <v>682</v>
       </c>
     </row>
     <row r="14">
@@ -3754,13 +3754,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>133</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15">
@@ -3768,13 +3768,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16">
@@ -3782,13 +3782,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17">
@@ -3796,13 +3796,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
@@ -3813,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -3841,10 +3841,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3897,13 +3897,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14749</v>
+        <v>14780</v>
       </c>
       <c r="C2" t="n">
-        <v>2199</v>
+        <v>2376</v>
       </c>
       <c r="D2" t="n">
-        <v>25774</v>
+        <v>25196</v>
       </c>
     </row>
     <row r="3">
@@ -3914,10 +3914,10 @@
         <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D3" t="n">
-        <v>14444</v>
+        <v>14295</v>
       </c>
     </row>
     <row r="4">
@@ -3925,13 +3925,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D4" t="n">
-        <v>11984</v>
+        <v>11901</v>
       </c>
     </row>
     <row r="5">
@@ -3939,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" t="n">
-        <v>3521</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="6">
@@ -3953,13 +3953,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C6" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D6" t="n">
-        <v>2641</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="7">
@@ -3967,13 +3967,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D7" t="n">
-        <v>2453</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="8">
@@ -3981,13 +3981,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8" t="n">
-        <v>2246</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="9">
@@ -3995,13 +3995,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>2026</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="10">
@@ -4009,13 +4009,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" t="n">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="11">
@@ -4029,7 +4029,7 @@
         <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>1581</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="12">
@@ -4043,7 +4043,7 @@
         <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>1335</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="13">
@@ -4051,13 +4051,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="14">
@@ -4065,13 +4065,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>964</v>
+        <v>985</v>
       </c>
     </row>
     <row r="15">
@@ -4079,13 +4079,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="16">
@@ -4093,13 +4093,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>698</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17">
@@ -4107,13 +4107,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>522</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18">
@@ -4121,13 +4121,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19">
@@ -4135,13 +4135,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>262</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20">
@@ -4149,13 +4149,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>106</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21">
@@ -4163,13 +4163,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4211,10 +4211,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>37690</v>
+        <v>34337</v>
       </c>
       <c r="D2" t="n">
-        <v>159444</v>
+        <v>155886</v>
       </c>
     </row>
     <row r="3">
@@ -4225,10 +4225,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>19709</v>
+        <v>18090</v>
       </c>
       <c r="D3" t="n">
-        <v>93404</v>
+        <v>88236</v>
       </c>
     </row>
     <row r="4">
@@ -4236,13 +4236,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>15596</v>
+        <v>13766</v>
       </c>
       <c r="D4" t="n">
-        <v>50212</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="5">
@@ -4250,13 +4250,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>11565</v>
+        <v>9516</v>
       </c>
       <c r="D5" t="n">
-        <v>22429</v>
+        <v>19999</v>
       </c>
     </row>
     <row r="6">
@@ -4264,13 +4264,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>8268</v>
+        <v>6714</v>
       </c>
       <c r="D6" t="n">
-        <v>8490</v>
+        <v>8907</v>
       </c>
     </row>
     <row r="7">
@@ -4278,13 +4278,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>5828</v>
+        <v>4924</v>
       </c>
       <c r="D7" t="n">
-        <v>3287</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="8">
@@ -4292,13 +4292,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C8" t="n">
-        <v>3821</v>
+        <v>3398</v>
       </c>
       <c r="D8" t="n">
-        <v>1909</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="9">
@@ -4306,13 +4306,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>212</v>
       </c>
       <c r="C9" t="n">
-        <v>2033</v>
+        <v>2181</v>
       </c>
       <c r="D9" t="n">
-        <v>1460</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="10">
@@ -4320,13 +4320,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>803</v>
+        <v>1145</v>
       </c>
       <c r="D10" t="n">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="11">
@@ -4334,13 +4334,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C11" t="n">
-        <v>239</v>
+        <v>499</v>
       </c>
       <c r="D11" t="n">
-        <v>775</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12">
@@ -4348,13 +4348,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="D12" t="n">
-        <v>486</v>
+        <v>793</v>
       </c>
     </row>
     <row r="13">
@@ -4362,13 +4362,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>263</v>
+        <v>675</v>
       </c>
     </row>
     <row r="14">
@@ -4376,13 +4376,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15">
@@ -4390,13 +4390,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16">
@@ -4404,13 +4404,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17">
@@ -4418,13 +4418,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18">
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -4463,10 +4463,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -4477,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4522,10 +4522,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>30197</v>
+        <v>28080</v>
       </c>
       <c r="D2" t="n">
-        <v>175743</v>
+        <v>169260</v>
       </c>
     </row>
     <row r="3">
@@ -4536,10 +4536,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>22254</v>
+        <v>19690</v>
       </c>
       <c r="D3" t="n">
-        <v>92319</v>
+        <v>87106</v>
       </c>
     </row>
     <row r="4">
@@ -4547,13 +4547,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16337</v>
+        <v>14302</v>
       </c>
       <c r="D4" t="n">
-        <v>52070</v>
+        <v>44902</v>
       </c>
     </row>
     <row r="5">
@@ -4561,13 +4561,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>12291</v>
+        <v>10032</v>
       </c>
       <c r="D5" t="n">
-        <v>23080</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="6">
@@ -4575,13 +4575,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>9035</v>
+        <v>7141</v>
       </c>
       <c r="D6" t="n">
-        <v>9015</v>
+        <v>9357</v>
       </c>
     </row>
     <row r="7">
@@ -4589,13 +4589,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>6303</v>
+        <v>5259</v>
       </c>
       <c r="D7" t="n">
-        <v>3425</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C8" t="n">
-        <v>4210</v>
+        <v>3644</v>
       </c>
       <c r="D8" t="n">
-        <v>1890</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="9">
@@ -4617,13 +4617,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="C9" t="n">
-        <v>2314</v>
+        <v>2387</v>
       </c>
       <c r="D9" t="n">
-        <v>1435</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="10">
@@ -4631,13 +4631,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="C10" t="n">
-        <v>963</v>
+        <v>1346</v>
       </c>
       <c r="D10" t="n">
-        <v>1032</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="11">
@@ -4645,13 +4645,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>285</v>
+        <v>615</v>
       </c>
       <c r="D11" t="n">
-        <v>748</v>
+        <v>918</v>
       </c>
     </row>
     <row r="12">
@@ -4659,13 +4659,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>248</v>
       </c>
       <c r="D12" t="n">
-        <v>457</v>
+        <v>783</v>
       </c>
     </row>
     <row r="13">
@@ -4673,13 +4673,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>239</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14">
@@ -4687,13 +4687,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15">
@@ -4701,13 +4701,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16">
@@ -4715,13 +4715,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17">
@@ -4729,13 +4729,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
@@ -4746,10 +4746,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
@@ -4760,10 +4760,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
@@ -4774,10 +4774,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4833,10 +4833,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>35248</v>
+        <v>31650</v>
       </c>
       <c r="D2" t="n">
-        <v>162936</v>
+        <v>156205</v>
       </c>
     </row>
     <row r="3">
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>22303</v>
+        <v>19650</v>
       </c>
       <c r="D3" t="n">
-        <v>93150</v>
+        <v>86728</v>
       </c>
     </row>
     <row r="4">
@@ -4858,13 +4858,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>17417</v>
+        <v>14816</v>
       </c>
       <c r="D4" t="n">
-        <v>52805</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="5">
@@ -4872,13 +4872,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>12928</v>
+        <v>10587</v>
       </c>
       <c r="D5" t="n">
-        <v>23991</v>
+        <v>21164</v>
       </c>
     </row>
     <row r="6">
@@ -4886,13 +4886,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C6" t="n">
-        <v>9649</v>
+        <v>7524</v>
       </c>
       <c r="D6" t="n">
-        <v>9322</v>
+        <v>9805</v>
       </c>
     </row>
     <row r="7">
@@ -4900,13 +4900,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>6870</v>
+        <v>5522</v>
       </c>
       <c r="D7" t="n">
-        <v>3570</v>
+        <v>4354</v>
       </c>
     </row>
     <row r="8">
@@ -4914,13 +4914,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C8" t="n">
-        <v>4577</v>
+        <v>3923</v>
       </c>
       <c r="D8" t="n">
-        <v>1871</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="9">
@@ -4928,13 +4928,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="C9" t="n">
-        <v>2577</v>
+        <v>2573</v>
       </c>
       <c r="D9" t="n">
-        <v>1420</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="10">
@@ -4942,13 +4942,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="C10" t="n">
-        <v>1104</v>
+        <v>1512</v>
       </c>
       <c r="D10" t="n">
-        <v>1006</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11">
@@ -4956,13 +4956,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="C11" t="n">
-        <v>336</v>
+        <v>744</v>
       </c>
       <c r="D11" t="n">
-        <v>720</v>
+        <v>905</v>
       </c>
     </row>
     <row r="12">
@@ -4970,13 +4970,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>307</v>
       </c>
       <c r="D12" t="n">
-        <v>429</v>
+        <v>773</v>
       </c>
     </row>
     <row r="13">
@@ -4984,13 +4984,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="D13" t="n">
-        <v>216</v>
+        <v>659</v>
       </c>
     </row>
     <row r="14">
@@ -4998,13 +4998,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15">
@@ -5012,13 +5012,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16">
@@ -5026,13 +5026,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17">
@@ -5040,13 +5040,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19">
@@ -5071,10 +5071,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -5085,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -5144,10 +5144,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>53209</v>
+        <v>45408</v>
       </c>
       <c r="D2" t="n">
-        <v>195106</v>
+        <v>181884</v>
       </c>
     </row>
     <row r="3">
@@ -5158,10 +5158,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>23039</v>
+        <v>20090</v>
       </c>
       <c r="D3" t="n">
-        <v>91879</v>
+        <v>86593</v>
       </c>
     </row>
     <row r="4">
@@ -5169,13 +5169,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>18180</v>
+        <v>15105</v>
       </c>
       <c r="D4" t="n">
-        <v>54030</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="5">
@@ -5183,13 +5183,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>13607</v>
+        <v>10934</v>
       </c>
       <c r="D5" t="n">
-        <v>24368</v>
+        <v>21487</v>
       </c>
     </row>
     <row r="6">
@@ -5197,13 +5197,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>10330</v>
+        <v>7977</v>
       </c>
       <c r="D6" t="n">
-        <v>9735</v>
+        <v>10144</v>
       </c>
     </row>
     <row r="7">
@@ -5211,13 +5211,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>7330</v>
+        <v>5764</v>
       </c>
       <c r="D7" t="n">
-        <v>3626</v>
+        <v>4534</v>
       </c>
     </row>
     <row r="8">
@@ -5225,13 +5225,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C8" t="n">
-        <v>4957</v>
+        <v>4126</v>
       </c>
       <c r="D8" t="n">
-        <v>1866</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="9">
@@ -5239,13 +5239,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C9" t="n">
-        <v>2836</v>
+        <v>2784</v>
       </c>
       <c r="D9" t="n">
-        <v>1391</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="10">
@@ -5253,13 +5253,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C10" t="n">
-        <v>1244</v>
+        <v>1658</v>
       </c>
       <c r="D10" t="n">
-        <v>987</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="11">
@@ -5267,13 +5267,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="C11" t="n">
-        <v>388</v>
+        <v>857</v>
       </c>
       <c r="D11" t="n">
-        <v>685</v>
+        <v>893</v>
       </c>
     </row>
     <row r="12">
@@ -5281,13 +5281,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>373</v>
       </c>
       <c r="D12" t="n">
-        <v>401</v>
+        <v>764</v>
       </c>
     </row>
     <row r="13">
@@ -5295,13 +5295,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="D13" t="n">
-        <v>195</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14">
@@ -5309,13 +5309,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15">
@@ -5323,13 +5323,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
@@ -5337,13 +5337,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17">
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
@@ -5368,10 +5368,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
@@ -5382,10 +5382,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -5396,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -5410,10 +5410,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5455,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>51922</v>
+        <v>44460</v>
       </c>
       <c r="D2" t="n">
-        <v>160288</v>
+        <v>150112</v>
       </c>
     </row>
     <row r="3">
@@ -5469,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>27042</v>
+        <v>22353</v>
       </c>
       <c r="D3" t="n">
-        <v>93158</v>
+        <v>86248</v>
       </c>
     </row>
     <row r="4">
@@ -5483,10 +5483,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>18828</v>
+        <v>15507</v>
       </c>
       <c r="D4" t="n">
-        <v>54204</v>
+        <v>45826</v>
       </c>
     </row>
     <row r="5">
@@ -5494,13 +5494,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>14201</v>
+        <v>11177</v>
       </c>
       <c r="D5" t="n">
-        <v>25000</v>
+        <v>21789</v>
       </c>
     </row>
     <row r="6">
@@ -5508,13 +5508,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>10854</v>
+        <v>8272</v>
       </c>
       <c r="D6" t="n">
-        <v>9948</v>
+        <v>10475</v>
       </c>
     </row>
     <row r="7">
@@ -5522,13 +5522,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>7869</v>
+        <v>6073</v>
       </c>
       <c r="D7" t="n">
-        <v>3668</v>
+        <v>4718</v>
       </c>
     </row>
     <row r="8">
@@ -5536,13 +5536,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>5305</v>
+        <v>4300</v>
       </c>
       <c r="D8" t="n">
-        <v>1841</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="9">
@@ -5550,13 +5550,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C9" t="n">
-        <v>3070</v>
+        <v>2938</v>
       </c>
       <c r="D9" t="n">
-        <v>1362</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="10">
@@ -5564,13 +5564,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C10" t="n">
-        <v>1364</v>
+        <v>1801</v>
       </c>
       <c r="D10" t="n">
-        <v>966</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="11">
@@ -5578,13 +5578,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>427</v>
+        <v>973</v>
       </c>
       <c r="D11" t="n">
-        <v>655</v>
+        <v>880</v>
       </c>
     </row>
     <row r="12">
@@ -5592,13 +5592,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="D12" t="n">
-        <v>372</v>
+        <v>753</v>
       </c>
     </row>
     <row r="13">
@@ -5606,13 +5606,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14">
@@ -5620,13 +5620,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15">
@@ -5634,13 +5634,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16">
@@ -5648,13 +5648,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -5665,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
@@ -5679,10 +5679,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19">
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -5721,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -5766,10 +5766,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>61711</v>
+        <v>51235</v>
       </c>
       <c r="D2" t="n">
-        <v>179779</v>
+        <v>165601</v>
       </c>
     </row>
     <row r="3">
@@ -5780,10 +5780,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>29231</v>
+        <v>23857</v>
       </c>
       <c r="D3" t="n">
-        <v>92653</v>
+        <v>84662</v>
       </c>
     </row>
     <row r="4">
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>20092</v>
+        <v>16152</v>
       </c>
       <c r="D4" t="n">
-        <v>54425</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="5">
@@ -5805,13 +5805,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>14749</v>
+        <v>11395</v>
       </c>
       <c r="D5" t="n">
-        <v>25601</v>
+        <v>22071</v>
       </c>
     </row>
     <row r="6">
@@ -5819,13 +5819,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>11358</v>
+        <v>8526</v>
       </c>
       <c r="D6" t="n">
-        <v>10167</v>
+        <v>10900</v>
       </c>
     </row>
     <row r="7">
@@ -5833,13 +5833,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>8381</v>
+        <v>6355</v>
       </c>
       <c r="D7" t="n">
-        <v>3710</v>
+        <v>4849</v>
       </c>
     </row>
     <row r="8">
@@ -5847,13 +5847,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>5656</v>
+        <v>4474</v>
       </c>
       <c r="D8" t="n">
-        <v>1816</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="9">
@@ -5861,13 +5861,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C9" t="n">
-        <v>3265</v>
+        <v>3079</v>
       </c>
       <c r="D9" t="n">
-        <v>1343</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="10">
@@ -5875,13 +5875,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="C10" t="n">
-        <v>1507</v>
+        <v>1932</v>
       </c>
       <c r="D10" t="n">
-        <v>935</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="11">
@@ -5889,13 +5889,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>461</v>
+        <v>1084</v>
       </c>
       <c r="D11" t="n">
-        <v>625</v>
+        <v>868</v>
       </c>
     </row>
     <row r="12">
@@ -5903,13 +5903,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>500</v>
       </c>
       <c r="D12" t="n">
-        <v>344</v>
+        <v>742</v>
       </c>
     </row>
     <row r="13">
@@ -5917,13 +5917,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>211</v>
       </c>
       <c r="D13" t="n">
-        <v>153</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14">
@@ -5931,13 +5931,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
@@ -5945,13 +5945,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16">
@@ -5959,13 +5959,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -5976,10 +5976,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18">
@@ -5990,10 +5990,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
@@ -6004,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -6018,10 +6018,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -6032,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6077,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>77099</v>
+        <v>62510</v>
       </c>
       <c r="D2" t="n">
-        <v>185611</v>
+        <v>169241</v>
       </c>
     </row>
     <row r="3">
@@ -6091,10 +6091,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>32603</v>
+        <v>25615</v>
       </c>
       <c r="D3" t="n">
-        <v>92580</v>
+        <v>83323</v>
       </c>
     </row>
     <row r="4">
@@ -6105,10 +6105,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>21341</v>
+        <v>16615</v>
       </c>
       <c r="D4" t="n">
-        <v>54238</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="5">
@@ -6116,13 +6116,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>15314</v>
+        <v>11624</v>
       </c>
       <c r="D5" t="n">
-        <v>25652</v>
+        <v>22104</v>
       </c>
     </row>
     <row r="6">
@@ -6130,13 +6130,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>11807</v>
+        <v>8826</v>
       </c>
       <c r="D6" t="n">
-        <v>10491</v>
+        <v>11102</v>
       </c>
     </row>
     <row r="7">
@@ -6144,13 +6144,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>8756</v>
+        <v>6525</v>
       </c>
       <c r="D7" t="n">
-        <v>3652</v>
+        <v>4989</v>
       </c>
     </row>
     <row r="8">
@@ -6158,13 +6158,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>6002</v>
+        <v>4642</v>
       </c>
       <c r="D8" t="n">
-        <v>1805</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="9">
@@ -6172,13 +6172,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C9" t="n">
-        <v>3483</v>
+        <v>3208</v>
       </c>
       <c r="D9" t="n">
-        <v>1310</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="10">
@@ -6186,13 +6186,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="C10" t="n">
-        <v>1607</v>
+        <v>2069</v>
       </c>
       <c r="D10" t="n">
-        <v>904</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="11">
@@ -6200,13 +6200,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>485</v>
+        <v>1170</v>
       </c>
       <c r="D11" t="n">
-        <v>595</v>
+        <v>856</v>
       </c>
     </row>
     <row r="12">
@@ -6214,13 +6214,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>564</v>
       </c>
       <c r="D12" t="n">
-        <v>317</v>
+        <v>732</v>
       </c>
     </row>
     <row r="13">
@@ -6228,13 +6228,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="D13" t="n">
-        <v>134</v>
+        <v>636</v>
       </c>
     </row>
     <row r="14">
@@ -6242,13 +6242,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15">
@@ -6256,13 +6256,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16">
@@ -6270,13 +6270,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17">
@@ -6287,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
@@ -6301,10 +6301,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
@@ -6315,10 +6315,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6388,10 +6388,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>66710</v>
+        <v>55114</v>
       </c>
       <c r="D2" t="n">
-        <v>166008</v>
+        <v>151230</v>
       </c>
     </row>
     <row r="3">
@@ -6402,10 +6402,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>37384</v>
+        <v>28148</v>
       </c>
       <c r="D3" t="n">
-        <v>92746</v>
+        <v>82206</v>
       </c>
     </row>
     <row r="4">
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>22843</v>
+        <v>17160</v>
       </c>
       <c r="D4" t="n">
-        <v>54061</v>
+        <v>45207</v>
       </c>
     </row>
     <row r="5">
@@ -6427,13 +6427,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>15921</v>
+        <v>11829</v>
       </c>
       <c r="D5" t="n">
-        <v>25695</v>
+        <v>22121</v>
       </c>
     </row>
     <row r="6">
@@ -6441,13 +6441,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>12240</v>
+        <v>9087</v>
       </c>
       <c r="D6" t="n">
-        <v>10845</v>
+        <v>11293</v>
       </c>
     </row>
     <row r="7">
@@ -6455,13 +6455,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>9111</v>
+        <v>6687</v>
       </c>
       <c r="D7" t="n">
-        <v>3578</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="8">
@@ -6469,13 +6469,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>6328</v>
+        <v>4789</v>
       </c>
       <c r="D8" t="n">
-        <v>1775</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="9">
@@ -6483,13 +6483,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>3688</v>
+        <v>3326</v>
       </c>
       <c r="D9" t="n">
-        <v>1277</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="10">
@@ -6497,13 +6497,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="C10" t="n">
-        <v>1700</v>
+        <v>2193</v>
       </c>
       <c r="D10" t="n">
-        <v>879</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="11">
@@ -6511,13 +6511,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="C11" t="n">
-        <v>490</v>
+        <v>1252</v>
       </c>
       <c r="D11" t="n">
-        <v>559</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12">
@@ -6525,13 +6525,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>623</v>
       </c>
       <c r="D12" t="n">
-        <v>291</v>
+        <v>721</v>
       </c>
     </row>
     <row r="13">
@@ -6539,13 +6539,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>275</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>626</v>
       </c>
     </row>
     <row r="14">
@@ -6553,13 +6553,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15">
@@ -6567,13 +6567,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16">
@@ -6581,13 +6581,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17">
@@ -6598,10 +6598,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18">
@@ -6612,10 +6612,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
@@ -6626,10 +6626,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -6640,10 +6640,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6699,10 +6699,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>9114</v>
+        <v>10036</v>
       </c>
       <c r="D2" t="n">
-        <v>95503</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="3">
@@ -6710,13 +6710,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4516</v>
+        <v>4408</v>
       </c>
       <c r="C3" t="n">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="D3" t="n">
-        <v>14680</v>
+        <v>14366</v>
       </c>
     </row>
     <row r="4">
@@ -6724,13 +6724,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D4" t="n">
-        <v>11832</v>
+        <v>11654</v>
       </c>
     </row>
     <row r="5">
@@ -6738,13 +6738,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C5" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D5" t="n">
-        <v>4097</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="6">
@@ -6752,13 +6752,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C6" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D6" t="n">
-        <v>2661</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="7">
@@ -6766,13 +6766,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D7" t="n">
-        <v>2485</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="8">
@@ -6780,13 +6780,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D8" t="n">
-        <v>2288</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="9">
@@ -6794,13 +6794,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D9" t="n">
-        <v>2014</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="10">
@@ -6808,13 +6808,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D10" t="n">
-        <v>1765</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="11">
@@ -6825,10 +6825,10 @@
         <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>1571</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="12">
@@ -6839,10 +6839,10 @@
         <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>1324</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="13">
@@ -6850,13 +6850,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>1144</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="14">
@@ -6864,13 +6864,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>949</v>
+        <v>978</v>
       </c>
     </row>
     <row r="15">
@@ -6878,13 +6878,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
-        <v>825</v>
+        <v>842</v>
       </c>
     </row>
     <row r="16">
@@ -6892,13 +6892,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>663</v>
+        <v>723</v>
       </c>
     </row>
     <row r="17">
@@ -6906,13 +6906,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>492</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18">
@@ -6920,13 +6920,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
-        <v>358</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19">
@@ -6934,13 +6934,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
-        <v>204</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20">
@@ -6948,13 +6948,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21">
@@ -6962,13 +6962,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -7007,13 +7007,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2210</v>
+        <v>2554</v>
       </c>
       <c r="C2" t="n">
-        <v>6190</v>
+        <v>7036</v>
       </c>
       <c r="D2" t="n">
-        <v>102755</v>
+        <v>98683</v>
       </c>
     </row>
     <row r="3">
@@ -7021,13 +7021,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2424</v>
+        <v>2403</v>
       </c>
       <c r="C3" t="n">
-        <v>3298</v>
+        <v>3378</v>
       </c>
       <c r="D3" t="n">
-        <v>20464</v>
+        <v>19772</v>
       </c>
     </row>
     <row r="4">
@@ -7035,13 +7035,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1471</v>
+        <v>1396</v>
       </c>
       <c r="C4" t="n">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="D4" t="n">
-        <v>11718</v>
+        <v>11448</v>
       </c>
     </row>
     <row r="5">
@@ -7049,13 +7049,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C5" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D5" t="n">
-        <v>4605</v>
+        <v>4824</v>
       </c>
     </row>
     <row r="6">
@@ -7063,13 +7063,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>2713</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="7">
@@ -7077,13 +7077,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>2492</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D8" t="n">
-        <v>2354</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="9">
@@ -7105,13 +7105,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>2003</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="10">
@@ -7119,13 +7119,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D10" t="n">
-        <v>1768</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="11">
@@ -7136,10 +7136,10 @@
         <v>57</v>
       </c>
       <c r="C11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>1561</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="12">
@@ -7147,13 +7147,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>1313</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="13">
@@ -7161,13 +7161,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>1124</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="14">
@@ -7175,13 +7175,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>942</v>
+        <v>972</v>
       </c>
     </row>
     <row r="15">
@@ -7189,13 +7189,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D15" t="n">
-        <v>802</v>
+        <v>835</v>
       </c>
     </row>
     <row r="16">
@@ -7203,13 +7203,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>628</v>
+        <v>717</v>
       </c>
     </row>
     <row r="17">
@@ -7217,13 +7217,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
-        <v>459</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18">
@@ -7231,13 +7231,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
-        <v>312</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19">
@@ -7245,13 +7245,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>150</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20">
@@ -7259,13 +7259,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
@@ -7273,13 +7273,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -7318,13 +7318,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>372</v>
+        <v>2230</v>
       </c>
       <c r="C2" t="n">
-        <v>11157</v>
+        <v>12231</v>
       </c>
       <c r="D2" t="n">
-        <v>171120</v>
+        <v>163370</v>
       </c>
     </row>
     <row r="3">
@@ -7332,13 +7332,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1969</v>
+        <v>2066</v>
       </c>
       <c r="C3" t="n">
-        <v>3862</v>
+        <v>4134</v>
       </c>
       <c r="D3" t="n">
-        <v>25901</v>
+        <v>24977</v>
       </c>
     </row>
     <row r="4">
@@ -7346,13 +7346,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1599</v>
+        <v>1489</v>
       </c>
       <c r="C4" t="n">
-        <v>1484</v>
+        <v>1381</v>
       </c>
       <c r="D4" t="n">
-        <v>12313</v>
+        <v>11789</v>
       </c>
     </row>
     <row r="5">
@@ -7360,13 +7360,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="C5" t="n">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="D5" t="n">
-        <v>5011</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="6">
@@ -7374,13 +7374,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C6" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D6" t="n">
-        <v>2835</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="7">
@@ -7388,13 +7388,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D7" t="n">
-        <v>2501</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="8">
@@ -7402,13 +7402,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D8" t="n">
-        <v>2396</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="9">
@@ -7416,13 +7416,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D9" t="n">
-        <v>2016</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="10">
@@ -7430,13 +7430,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D10" t="n">
-        <v>1770</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="11">
@@ -7444,13 +7444,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>1551</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="12">
@@ -7458,13 +7458,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>1301</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="13">
@@ -7472,13 +7472,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>1106</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="14">
@@ -7486,13 +7486,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>932</v>
+        <v>966</v>
       </c>
     </row>
     <row r="15">
@@ -7500,13 +7500,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>776</v>
+        <v>829</v>
       </c>
     </row>
     <row r="16">
@@ -7514,13 +7514,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>593</v>
+        <v>711</v>
       </c>
     </row>
     <row r="17">
@@ -7528,13 +7528,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D17" t="n">
-        <v>421</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18">
@@ -7542,13 +7542,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D18" t="n">
-        <v>262</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19">
@@ -7556,13 +7556,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>106</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20">
@@ -7570,13 +7570,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
@@ -7584,13 +7584,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -7629,13 +7629,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2227</v>
+        <v>4366</v>
       </c>
       <c r="C2" t="n">
-        <v>8182</v>
+        <v>9344</v>
       </c>
       <c r="D2" t="n">
-        <v>164190</v>
+        <v>157558</v>
       </c>
     </row>
     <row r="3">
@@ -7643,13 +7643,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>925</v>
+        <v>1493</v>
       </c>
       <c r="C3" t="n">
-        <v>5402</v>
+        <v>5531</v>
       </c>
       <c r="D3" t="n">
-        <v>34046</v>
+        <v>31632</v>
       </c>
     </row>
     <row r="4">
@@ -7657,13 +7657,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1065</v>
+        <v>1004</v>
       </c>
       <c r="C4" t="n">
-        <v>1932</v>
+        <v>1852</v>
       </c>
       <c r="D4" t="n">
-        <v>11549</v>
+        <v>10756</v>
       </c>
     </row>
     <row r="5">
@@ -7671,13 +7671,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>492</v>
+        <v>447</v>
       </c>
       <c r="C5" t="n">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="D5" t="n">
-        <v>4410</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="6">
@@ -7685,13 +7685,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D6" t="n">
-        <v>2324</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="7">
@@ -7699,13 +7699,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D7" t="n">
-        <v>1901</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="8">
@@ -7713,13 +7713,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D8" t="n">
-        <v>1814</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="9">
@@ -7727,13 +7727,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D9" t="n">
-        <v>1449</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="10">
@@ -7741,13 +7741,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
-        <v>1261</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="11">
@@ -7755,13 +7755,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>1083</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="12">
@@ -7769,13 +7769,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>896</v>
+        <v>918</v>
       </c>
     </row>
     <row r="13">
@@ -7783,13 +7783,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>750</v>
+        <v>781</v>
       </c>
     </row>
     <row r="14">
@@ -7797,13 +7797,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>628</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15">
@@ -7811,13 +7811,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>507</v>
+        <v>565</v>
       </c>
     </row>
     <row r="16">
@@ -7825,13 +7825,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>376</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17">
@@ -7839,13 +7839,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>254</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18">
@@ -7853,13 +7853,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>142</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19">
@@ -7867,13 +7867,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20">
@@ -7881,13 +7881,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21">
@@ -7895,13 +7895,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -7943,10 +7943,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7221</v>
+        <v>8195</v>
       </c>
       <c r="D2" t="n">
-        <v>176455</v>
+        <v>172358</v>
       </c>
     </row>
     <row r="3">
@@ -7954,13 +7954,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1302</v>
+        <v>2315</v>
       </c>
       <c r="C3" t="n">
-        <v>5931</v>
+        <v>6327</v>
       </c>
       <c r="D3" t="n">
-        <v>46824</v>
+        <v>42805</v>
       </c>
     </row>
     <row r="4">
@@ -7968,13 +7968,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>884</v>
+        <v>1059</v>
       </c>
       <c r="C4" t="n">
-        <v>3575</v>
+        <v>3455</v>
       </c>
       <c r="D4" t="n">
-        <v>14116</v>
+        <v>12931</v>
       </c>
     </row>
     <row r="5">
@@ -7982,13 +7982,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>676</v>
+        <v>620</v>
       </c>
       <c r="C5" t="n">
-        <v>1149</v>
+        <v>1057</v>
       </c>
       <c r="D5" t="n">
-        <v>5029</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="6">
@@ -7996,13 +7996,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="D6" t="n">
-        <v>2518</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="7">
@@ -8010,13 +8010,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D7" t="n">
-        <v>1952</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="8">
@@ -8024,13 +8024,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>1817</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="9">
@@ -8038,13 +8038,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>1483</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="10">
@@ -8052,13 +8052,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>1278</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="11">
@@ -8066,13 +8066,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>1078</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12">
@@ -8080,13 +8080,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>888</v>
+        <v>916</v>
       </c>
     </row>
     <row r="13">
@@ -8094,13 +8094,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>746</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14">
@@ -8111,10 +8111,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>612</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15">
@@ -8122,13 +8122,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>488</v>
+        <v>562</v>
       </c>
     </row>
     <row r="16">
@@ -8136,13 +8136,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>352</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17">
@@ -8150,13 +8150,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>227</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18">
@@ -8164,13 +8164,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>112</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19">
@@ -8178,13 +8178,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20">
@@ -8192,13 +8192,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
@@ -8206,13 +8206,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -8254,10 +8254,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3870</v>
+        <v>4720</v>
       </c>
       <c r="D2" t="n">
-        <v>135526</v>
+        <v>132379</v>
       </c>
     </row>
     <row r="3">
@@ -8265,13 +8265,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1478</v>
+        <v>2423</v>
       </c>
       <c r="C3" t="n">
-        <v>7373</v>
+        <v>7931</v>
       </c>
       <c r="D3" t="n">
-        <v>52765</v>
+        <v>48594</v>
       </c>
     </row>
     <row r="4">
@@ -8279,13 +8279,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="C4" t="n">
-        <v>4243</v>
+        <v>3822</v>
       </c>
       <c r="D4" t="n">
-        <v>13410</v>
+        <v>12437</v>
       </c>
     </row>
     <row r="5">
@@ -8293,13 +8293,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="C5" t="n">
-        <v>809</v>
+        <v>752</v>
       </c>
       <c r="D5" t="n">
-        <v>4724</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="6">
@@ -8307,13 +8307,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>2455</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="7">
@@ -8321,13 +8321,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D7" t="n">
-        <v>1780</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="8">
@@ -8335,13 +8335,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>1453</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="9">
@@ -8349,13 +8349,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D9" t="n">
-        <v>1252</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="10">
@@ -8363,13 +8363,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>1056</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="11">
@@ -8377,13 +8377,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>870</v>
+        <v>897</v>
       </c>
     </row>
     <row r="12">
@@ -8391,13 +8391,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>731</v>
+        <v>764</v>
       </c>
     </row>
     <row r="13">
@@ -8408,10 +8408,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
     </row>
     <row r="14">
@@ -8419,13 +8419,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>478</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15">
@@ -8433,13 +8433,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>344</v>
+        <v>465</v>
       </c>
     </row>
     <row r="16">
@@ -8447,13 +8447,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>222</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17">
@@ -8461,13 +8461,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>109</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18">
@@ -8475,13 +8475,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
@@ -8489,13 +8489,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
@@ -8503,13 +8503,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -8565,10 +8565,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1754</v>
+        <v>2226</v>
       </c>
       <c r="D2" t="n">
-        <v>101207</v>
+        <v>100237</v>
       </c>
     </row>
     <row r="3">
@@ -8576,13 +8576,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>692</v>
+        <v>1217</v>
       </c>
       <c r="C3" t="n">
-        <v>5210</v>
+        <v>5923</v>
       </c>
       <c r="D3" t="n">
-        <v>59754</v>
+        <v>54819</v>
       </c>
     </row>
     <row r="4">
@@ -8590,13 +8590,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1142</v>
+        <v>1430</v>
       </c>
       <c r="C4" t="n">
-        <v>5860</v>
+        <v>5706</v>
       </c>
       <c r="D4" t="n">
-        <v>17922</v>
+        <v>16462</v>
       </c>
     </row>
     <row r="5">
@@ -8604,13 +8604,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C5" t="n">
-        <v>2256</v>
+        <v>2003</v>
       </c>
       <c r="D5" t="n">
-        <v>5428</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="6">
@@ -8618,13 +8618,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C6" t="n">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D6" t="n">
-        <v>2646</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="7">
@@ -8632,13 +8632,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D7" t="n">
-        <v>1839</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="8">
@@ -8646,13 +8646,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D8" t="n">
-        <v>1519</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="9">
@@ -8663,10 +8663,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>1315</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="10">
@@ -8674,13 +8674,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11">
@@ -8688,13 +8688,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>930</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12">
@@ -8705,10 +8705,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>773</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13">
@@ -8716,13 +8716,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>468</v>
+        <v>672</v>
       </c>
     </row>
     <row r="14">
@@ -8730,13 +8730,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>337</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15">
@@ -8744,13 +8744,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>217</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16">
@@ -8758,13 +8758,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>106</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17">
@@ -8772,13 +8772,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18">
@@ -8786,13 +8786,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -8800,13 +8800,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
